--- a/Trắc nghiệm ôn luyện/BA Technical/multiple_choice_sample_template_UIUX_WIREFRAMING.xlsx
+++ b/Trắc nghiệm ôn luyện/BA Technical/multiple_choice_sample_template_UIUX_WIREFRAMING.xlsx
@@ -453,19 +453,19 @@
         <v>Wireframe tập trung vào bố cục, phân bổ thông tin (layout). Mockup tập trung vào phần nhìn (visual design) bao gồm màu sắc, font chữ và nhận diện thương hiệu.</v>
       </c>
       <c r="E2" t="str">
+        <v>Wireframe chỉ chạy được trên điện thoại Android; Mockup chỉ chạy được trên iPhone — nền tảng hỗ trợ</v>
+      </c>
+      <c r="F2" t="str">
         <v>Wireframe là bản vẽ khung xương đen trắng cấu trúc trang; Mockup là thiết kế tĩnh có màu sắc, hình ảnh và typography chân thực — cấu trúc vs trực quan</v>
       </c>
-      <c r="F2" t="str">
+      <c r="G2" t="str">
+        <v>Wireframe dùng để kiểm thử lỗi bảo mật; Mockup dùng để đo lường tốc độ tải trang — mục đích kỹ thuật</v>
+      </c>
+      <c r="H2" t="str">
         <v>Wireframe do Dev vẽ bằng code; Mockup do khách hàng tự vẽ bằng bút chì trên giấy — chủ thể vẽ</v>
       </c>
-      <c r="G2" t="str">
-        <v>Wireframe chỉ chạy được trên điện thoại Android; Mockup chỉ chạy được trên iPhone — nền tảng hỗ trợ</v>
-      </c>
-      <c r="H2" t="str">
-        <v>Wireframe dùng để kiểm thử lỗi bảo mật; Mockup dùng để đo lường tốc độ tải trang — mục đích kỹ thuật</v>
-      </c>
       <c r="I2">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -485,13 +485,13 @@
         <v>Chuỗi các bước liên tiếp mà người dùng thực hiện trên giao diện để hoàn thành một mục tiêu cụ thể — luồng hành vi giao diện</v>
       </c>
       <c r="F3" t="str">
+        <v>Biểu đồ thể hiện dung lượng bộ nhớ RAM tiêu thụ khi mở một trang web — hiệu năng hệ thống</v>
+      </c>
+      <c r="G3" t="str">
+        <v>Sơ đồ phân quyền các nhóm người dùng trong cơ sở dữ liệu SQL — phân quyền người dùng</v>
+      </c>
+      <c r="H3" t="str">
         <v>Tốc độ di chuyển của chuột máy tính khi người dùng rê qua các nút bấm — tốc độ di trỏ chuột</v>
-      </c>
-      <c r="G3" t="str">
-        <v>Biểu đồ thể hiện dung lượng bộ nhớ RAM tiêu thụ khi mở một trang web — hiệu năng hệ thống</v>
-      </c>
-      <c r="H3" t="str">
-        <v>Sơ đồ phân quyền các nhóm người dùng trong cơ sở dữ liệu SQL — phân quyền người dùng</v>
       </c>
       <c r="I3">
         <v>1</v>
@@ -511,19 +511,19 @@
         <v>Định luật Fitts chỉ ra rằng thời gian để đạt được một mục tiêu phụ thuộc vào khoảng cách và kích thước của mục tiêu đó. Nút bấm quan trọng cần thiết kế to và đặt ở vị trí dễ chạm tới.</v>
       </c>
       <c r="E4" t="str">
+        <v>Màu sắc của nút bấm bắt buộc phải là màu đỏ để thu hút sự chú ý của người dùng — quy định màu sắc nút</v>
+      </c>
+      <c r="F4" t="str">
+        <v>Nút bấm phải hiển thị kèm theo âm thanh click khi người dùng nhấn vào — âm thanh phản hồi</v>
+      </c>
+      <c r="G4" t="str">
         <v>Kích thước nút bấm phải đủ lớn và khoảng cách di chuyển chuột đến nút phải đủ ngắn để dễ dàng tương tác — tối ưu hóa thao tác bấm</v>
-      </c>
-      <c r="F4" t="str">
-        <v>Màu sắc của nút bấm bắt buộc phải là màu đỏ để thu hút sự chú ý của người dùng — quy định màu sắc nút</v>
-      </c>
-      <c r="G4" t="str">
-        <v>Nút bấm phải hiển thị kèm theo âm thanh click khi người dùng nhấn vào — âm thanh phản hồi</v>
       </c>
       <c r="H4" t="str">
         <v>Mỗi màn hình chỉ được phép chứa duy nhất một nút bấm duy nhất để tránh nhầm lẫn — giới hạn số nút</v>
       </c>
       <c r="I4">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -540,19 +540,19 @@
         <v>CTA là nút bấm quan trọng nhất trên màn hình, được thiết kế nổi bật (màu sắc tương phản tốt) nhằm định hướng hành vi của người dùng thực hiện chuyển đổi.</v>
       </c>
       <c r="E5" t="str">
+        <v>Icon hình chiếc điện thoại dùng để khách hàng bấm gọi trực tiếp cho tổng đài — nút gọi điện</v>
+      </c>
+      <c r="F5" t="str">
+        <v>Form nhập thông tin thẻ ngân hàng để thanh toán hóa đơn — form thanh toán</v>
+      </c>
+      <c r="G5" t="str">
         <v>Nút bấm hoặc liên kết nổi bật thúc giục người dùng thực hiện một hành động mục tiêu (như "Đăng ký ngay", "Mua hàng") — phần tử kích hoạt hành động</v>
       </c>
-      <c r="F5" t="str">
+      <c r="H5" t="str">
         <v>Khung hiển thị điều khoản sử dụng dài 10 trang buộc người dùng phải đọc — điều khoản pháp lý</v>
       </c>
-      <c r="G5" t="str">
-        <v>Form nhập thông tin thẻ ngân hàng để thanh toán hóa đơn — form thanh toán</v>
-      </c>
-      <c r="H5" t="str">
-        <v>Icon hình chiếc điện thoại dùng để khách hàng bấm gọi trực tiếp cho tổng đài — nút gọi điện</v>
-      </c>
       <c r="I5">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -569,19 +569,19 @@
         <v>Khoảng trắng không phải là khoảng trống vô nghĩa. Nó là công cụ thiết kế giúp nhóm các phần tử liên quan (Proximity), cải thiện độ đọc và giảm tải nhận thức cho người dùng.</v>
       </c>
       <c r="E6" t="str">
-        <v>Giúp giao diện không bị rối mắt, tạo khoảng thở cho các phần tử và làm nổi bật các nội dung quan trọng — tăng tính rõ ràng và tập trung</v>
+        <v>Để tiết kiệm mực in khi BA in tài liệu Wireframe ra giấy cho khách hàng xem — tiết kiệm mực in</v>
       </c>
       <c r="F6" t="str">
         <v>Để giảm thiểu dung lượng file ảnh khi lưu trữ trên máy tính của thiết kế — tiết kiệm bộ nhớ</v>
       </c>
       <c r="G6" t="str">
-        <v>Để tiết kiệm mực in khi BA in tài liệu Wireframe ra giấy cho khách hàng xem — tiết kiệm mực in</v>
+        <v>Vì lập trình viên không biết viết code để lấp đầy các khoảng trống đó — hạn chế kỹ thuật</v>
       </c>
       <c r="H6" t="str">
-        <v>Vì lập trình viên không biết viết code để lấp đầy các khoảng trống đó — hạn chế kỹ thuật</v>
+        <v>Giúp giao diện không bị rối mắt, tạo khoảng thở cho các phần tử và làm nổi bật các nội dung quan trọng — tăng tính rõ ràng và tập trung</v>
       </c>
       <c r="I6">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
@@ -598,19 +598,19 @@
         <v>Mobile-First buộc thiết kế tập trung vào những tính năng cốt lõi nhất do giới hạn về không gian màn hình điện thoại, sau đó mới mở rộng dần (Progressive Enhancement) sang màn hình to.</v>
       </c>
       <c r="E7" t="str">
+        <v>Thiết kế giao diện cho đồng hồ thông minh (smartwatch) trước rồi mở rộng ra máy tính — đồng hồ trước</v>
+      </c>
+      <c r="F7" t="str">
+        <v>Thiết kế giao diện chạy trên màn hình tivi thông minh 55 inch trước rồi mới làm di động — tivi trước</v>
+      </c>
+      <c r="G7" t="str">
+        <v>Thiết kế giao diện cho màn hình máy tính bàn trước rồi co nhỏ lại cho điện thoại — máy tính trước</v>
+      </c>
+      <c r="H7" t="str">
         <v>Thiết kế giao diện cho thiết bị di động trước, sau đó mở rộng dần cho máy tính (desktop) — di động trước</v>
       </c>
-      <c r="F7" t="str">
-        <v>Thiết kế giao diện cho màn hình máy tính bàn trước rồi co nhỏ lại cho điện thoại — máy tính trước</v>
-      </c>
-      <c r="G7" t="str">
-        <v>Thiết kế giao diện cho đồng hồ thông minh (smartwatch) trước rồi mở rộng ra máy tính — đồng hồ trước</v>
-      </c>
-      <c r="H7" t="str">
-        <v>Thiết kế giao diện chạy trên màn hình tivi thông minh 55 inch trước rồi mới làm di động — tivi trước</v>
-      </c>
       <c r="I7">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
@@ -627,19 +627,19 @@
         <v>Breadcrumb (vệt bánh mì) giúp người dùng định vị vị trí hiện tại của mình trong cấu trúc phân cấp website và dễ dàng quay lại các thư mục cha.</v>
       </c>
       <c r="E8" t="str">
-        <v>Thanh điều hướng phân cấp (như Trang chủ &gt; Điện thoại &gt; iPhone) giúp người dùng biết mình đang ở đâu trong hệ thống — định vị phân cấp</v>
+        <v>Khung hiển thị các quảng cáo sản phẩm liên quan ở bên dưới trang chi tiết — khung quảng cáo</v>
       </c>
       <c r="F8" t="str">
-        <v>Khung hiển thị các quảng cáo sản phẩm liên quan ở bên dưới trang chi tiết — khung quảng cáo</v>
+        <v>Thông báo lỗi hệ thống hiển thị dạng popup giữa màn hình — popup báo lỗi</v>
       </c>
       <c r="G8" t="str">
         <v>Icon hình chiếc bánh mì dùng để người dùng bấm đặt đồ ăn trực tuyến — icon đặt đồ ăn</v>
       </c>
       <c r="H8" t="str">
-        <v>Thông báo lỗi hệ thống hiển thị dạng popup giữa màn hình — popup báo lỗi</v>
+        <v>Thanh điều hướng phân cấp (như Trang chủ &gt; Điện thoại &gt; iPhone) giúp người dùng biết mình đang ở đâu trong hệ thống — định vị phân cấp</v>
       </c>
       <c r="I8">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
@@ -659,13 +659,13 @@
         <v>Đại diện cho vị trí sẽ chèn hình ảnh sau này mà không cần đưa ảnh thật vào làm phân tâm — vị trí chèn ảnh</v>
       </c>
       <c r="F9" t="str">
+        <v>Biểu thị khu vực người dùng không được phép chạm vào trên màn hình — vùng cấm</v>
+      </c>
+      <c r="G9" t="str">
         <v>Biểu thị nút bấm đóng cửa sổ popup hoặc xóa dữ liệu — nút đóng/xóa</v>
       </c>
-      <c r="G9" t="str">
+      <c r="H9" t="str">
         <v>Đánh dấu vùng giao diện đang bị lỗi và cần lập trình viên sửa đổi — vùng lỗi kỹ thuật</v>
-      </c>
-      <c r="H9" t="str">
-        <v>Biểu thị khu vực người dùng không được phép chạm vào trên màn hình — vùng cấm</v>
       </c>
       <c r="I9">
         <v>1</v>
@@ -685,19 +685,19 @@
         <v>Multi-step Form giúp giảm thiểu tải nhận thức (Cognitive Load). Người dùng thấy form ngắn ở từng bước sẽ ít nản lòng hơn so với một form dài dằng dặc.</v>
       </c>
       <c r="E10" t="str">
+        <v>Hiển thị toàn bộ 20 trường trên 1 trang duy nhất để người dùng không phải bấm nút chuyển trang — hiển thị tập trung</v>
+      </c>
+      <c r="F10" t="str">
         <v>Chia form thành các bước tuần tự (Multi-step Form) có thanh tiến trình hiển thị rõ ràng, kết hợp ẩn bớt các trường không bắt buộc — chia nhỏ quy trình</v>
       </c>
-      <c r="F10" t="str">
-        <v>Hiển thị toàn bộ 20 trường trên 1 trang duy nhất để người dùng không phải bấm nút chuyển trang — hiển thị tập trung</v>
-      </c>
       <c r="G10" t="str">
+        <v>Yêu cầu người dùng phải chụp ảnh căn cước công dân tải lên trước khi được phép nhập form — xác thực sớm</v>
+      </c>
+      <c r="H10" t="str">
         <v>Tự động báo lỗi đỏ ở tất cả các trường ngay khi người dùng vừa mới mở trang web lên — báo lỗi sớm</v>
       </c>
-      <c r="H10" t="str">
-        <v>Yêu cầu người dùng phải chụp ảnh căn cước công dân tải lên trước khi được phép nhập form — xác thực sớm</v>
-      </c>
       <c r="I10">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -714,19 +714,19 @@
         <v>Định luật Proximity chỉ ra rằng bộ não con người có xu hướng gom các vật thể đặt gần nhau thành một nhóm có chung đặc tính. Áp dụng vào UI, BA cần phân bổ khoảng cách (margin/padding) hợp lý để nhóm thông tin.</v>
       </c>
       <c r="E11" t="str">
+        <v>Thiết kế giao diện chỉ sử dụng duy nhất một font chữ cho tất cả các tiêu đề và nội dung — đồng bộ font</v>
+      </c>
+      <c r="F11" t="str">
         <v>Các phần tử có mối quan hệ nghiệp vụ mật thiết với nhau cần được đặt gần nhau về mặt không gian địa lý để người dùng tự hiểu chúng thuộc cùng một nhóm — nhóm các phần tử liên quan</v>
-      </c>
-      <c r="F11" t="str">
-        <v>Đặt nút hủy giao dịch ngay sát nút xác nhận thanh toán để người dùng dễ chọn lựa nhanh chóng — đặt gần nút thao tác</v>
       </c>
       <c r="G11" t="str">
         <v>Tự động phóng to kích thước của hình ảnh sản phẩm lên gấp 5 lần khi di chuột qua — phóng to hình ảnh</v>
       </c>
       <c r="H11" t="str">
-        <v>Thiết kế giao diện chỉ sử dụng duy nhất một font chữ cho tất cả các tiêu đề và nội dung — đồng bộ font</v>
+        <v>Đặt nút hủy giao dịch ngay sát nút xác nhận thanh toán để người dùng dễ chọn lựa nhanh chóng — đặt gần nút thao tác</v>
       </c>
       <c r="I11">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -749,10 +749,10 @@
         <v>Mức giá tối đa mà khách hàng sẵn sàng trả tiền để mua bản quyền sử dụng phần mềm — khả năng chi trả tài chính</v>
       </c>
       <c r="G12" t="str">
+        <v>Tốc độ phản hồi trung bình của giao diện sau khi người dùng thực hiện một click chuột — tốc độ tương tác</v>
+      </c>
+      <c r="H12" t="str">
         <v>Tổng số lượng trang màn hình tối đa của một bản thiết kế Figma hoàn chỉnh — quy mô thiết kế</v>
-      </c>
-      <c r="H12" t="str">
-        <v>Tốc độ phản hồi trung bình của giao diện sau khi người dùng thực hiện một click chuột — tốc độ tương tác</v>
       </c>
       <c r="I12">
         <v>1</v>
@@ -772,19 +772,19 @@
         <v>Thiết kế trạng thái lỗi tốt giúp giảm tỷ lệ bỏ rơi ứng dụng. Thông báo lỗi mơ hồ kiểu "Đã có lỗi xảy ra" mà không chỉ rõ cách sửa sẽ làm người dùng ức chế và rời bỏ hệ thống.</v>
       </c>
       <c r="E13" t="str">
-        <v>Để chỉ ra rõ ràng lỗi xảy ra ở đâu, nguyên nhân là gì và hướng dẫn cụ thể cách khắc phục (ví dụ: mật khẩu thiếu ký tự số) để người dùng hoàn thành tác vụ — giải quyết tắc nghẽn trải nghiệm</v>
+        <v>Để hiển thị quảng cáo của các bên đối tác trong thời gian hệ thống tải trang báo lỗi — hiển thị quảng cáo</v>
       </c>
       <c r="F13" t="str">
         <v>Để hệ thống tự động trừ tiền phạt trong tài khoản của khách hàng khi họ nhập sai thông tin — phạt người dùng</v>
       </c>
       <c r="G13" t="str">
+        <v>Để chỉ ra rõ ràng lỗi xảy ra ở đâu, nguyên nhân là gì và hướng dẫn cụ thể cách khắc phục (ví dụ: mật khẩu thiếu ký tự số) để người dùng hoàn thành tác vụ — giải quyết tắc nghẽn trải nghiệm</v>
+      </c>
+      <c r="H13" t="str">
         <v>Để lập trình viên có thể đổ lỗi cho người dùng khi hệ thống gặp lỗi logic code — đổ lỗi cho người dùng</v>
       </c>
-      <c r="H13" t="str">
-        <v>Để hiển thị quảng cáo của các bên đối tác trong thời gian hệ thống tải trang báo lỗi — hiển thị quảng cáo</v>
-      </c>
       <c r="I13">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14">
@@ -801,19 +801,19 @@
         <v>Hệ thống lưới linh hoạt (Fluid Grid) là cốt lõi của Responsive Web Design, giúp giao diện tự thích ứng (adapt) mượt mà với mọi kích thước chiều rộng màn hình từ điện thoại, tablet đến desktop.</v>
       </c>
       <c r="E14" t="str">
-        <v>Grid cố định sử dụng đơn vị pixels (px) để định dạng chiều rộng; Grid linh hoạt sử dụng đơn vị phần trăm (%) để tự động co giãn theo kích thước màn hình — pixels vs phần trăm co giãn</v>
+        <v>Grid cố định tự động khóa màn hình của người dùng khi có cuộc gọi điện thoại đến — bảo mật cuộc gọi</v>
       </c>
       <c r="F14" t="str">
         <v>Grid cố định chỉ dùng cho thiết kế đen trắng; Grid linh hoạt bắt buộc phải có tối thiểu 12 màu sắc — phân biệt màu sắc lưới</v>
       </c>
       <c r="G14" t="str">
+        <v>Grid cố định sử dụng đơn vị pixels (px) để định dạng chiều rộng; Grid linh hoạt sử dụng đơn vị phần trăm (%) để tự động co giãn theo kích thước màn hình — pixels vs phần trăm co giãn</v>
+      </c>
+      <c r="H14" t="str">
         <v>Grid cố định do lập trình viên tự quyết định; Grid linh hoạt do BA vẽ bằng tay trên giấy — phân vai trò vẽ lưới</v>
       </c>
-      <c r="H14" t="str">
-        <v>Grid cố định tự động khóa màn hình của người dùng khi có cuộc gọi điện thoại đến — bảo mật cuộc gọi</v>
-      </c>
       <c r="I14">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15">
@@ -830,19 +830,19 @@
         <v>IA quyết định sơ đồ trang web (Sitemap), cách dán nhãn các danh mục (Menu labels) và luồng điều hướng. IA tốt giúp người dùng định hình được cấu trúc trang web và không bị lạc.</v>
       </c>
       <c r="E15" t="str">
+        <v>Bảng thống kê số lượng bài viết đăng tải trên trang tin tức hàng tháng — quản lý nội dung</v>
+      </c>
+      <c r="F15" t="str">
         <v>Cách thức tổ chức, phân cấp cấu trúc thông tin và sơ đồ điều hướng của website giúp người dùng tìm kiếm thông tin dễ dàng nhất — sơ đồ cấu trúc thông tin</v>
-      </c>
-      <c r="F15" t="str">
-        <v>Mô hình vật lý kết nối các máy chủ lưu trữ dữ liệu SQL của dự án — kiến trúc máy chủ</v>
       </c>
       <c r="G15" t="str">
         <v>Quy trình nén các tệp tin hình ảnh đồ họa để lưu trữ trên Cloud — quy trình nén ảnh</v>
       </c>
       <c r="H15" t="str">
-        <v>Bảng thống kê số lượng bài viết đăng tải trên trang tin tức hàng tháng — quản lý nội dung</v>
+        <v>Mô hình vật lý kết nối các máy chủ lưu trữ dữ liệu SQL của dự án — kiến trúc máy chủ</v>
       </c>
       <c r="I15">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -859,7 +859,7 @@
         <v>Inline Validation giúp người dùng sửa sai ngay lập tức tại thời điểm nhập, giảm thời gian và sự ức chế so với việc bấm Submit rồi mới thấy danh sách lỗi hiển thị.</v>
       </c>
       <c r="E16" t="str">
-        <v>Kiểm tra và báo lỗi dữ liệu ngay tại ô nhập liệu khi người dùng vừa rời khỏi ô đó, thay vì đợi bấm nút Submit mới báo lỗi — phản hồi thời gian thực</v>
+        <v>Bắt buộc người dùng phải nhập thông tin mật khẩu hai lần trước khi đăng ký — xác thực mật khẩu</v>
       </c>
       <c r="F16" t="str">
         <v>Tự động gửi email thông báo cho khách hàng mỗi khi họ nhập xong một ô thông tin — thông báo qua email</v>
@@ -868,10 +868,10 @@
         <v>Ẩn toàn bộ các ô nhập liệu khác và chỉ hiển thị ô đang bị lỗi trên màn hình — tập trung ô lỗi</v>
       </c>
       <c r="H16" t="str">
-        <v>Bắt buộc người dùng phải nhập thông tin mật khẩu hai lần trước khi đăng ký — xác thực mật khẩu</v>
+        <v>Kiểm tra và báo lỗi dữ liệu ngay tại ô nhập liệu khi người dùng vừa rời khỏi ô đó, thay vì đợi bấm nút Submit mới báo lỗi — phản hồi thời gian thực</v>
       </c>
       <c r="I16">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="17">
@@ -894,10 +894,10 @@
         <v>Radio Button dùng để nghe nhạc; Checkbox dùng để xem video trên trang web — phân loại đa phương tiện</v>
       </c>
       <c r="G17" t="str">
+        <v>Radio Button chỉ dùng trên điện thoại; Checkbox chỉ sử dụng trên màn hình máy tính — phân loại thiết bị</v>
+      </c>
+      <c r="H17" t="str">
         <v>Radio Button bắt buộc phải hiển thị dạng hình vuông; Checkbox hiển thị dạng hình tròn — hình dạng phần tử</v>
-      </c>
-      <c r="H17" t="str">
-        <v>Radio Button chỉ dùng trên điện thoại; Checkbox chỉ sử dụng trên màn hình máy tính — phân loại thiết bị</v>
       </c>
       <c r="I17">
         <v>1</v>
@@ -917,19 +917,19 @@
         <v>Skeleton Screen thay thế cho spinner quay tròn truyền thống. Bằng cách hiển thị trước khung xương bố cục, nó hướng sự chú ý của người dùng vào nội dung sắp tải, giúp giảm cảm giác chờ đợi mệt mỏi.</v>
       </c>
       <c r="E18" t="str">
+        <v>Biểu thị sơ đồ cấu trúc xương của nhân vật hoạt hình 3D trong game — đồ họa game 3D</v>
+      </c>
+      <c r="F18" t="str">
+        <v>Đại diện cho chế độ ban đêm (Dark Mode) của ứng dụng di động — chế độ ban đêm</v>
+      </c>
+      <c r="G18" t="str">
+        <v>Đánh dấu các khu vực giao diện đang bị khóa tính năng đối với tài khoản thường — khóa tính năng</v>
+      </c>
+      <c r="H18" t="str">
         <v>Biểu thị giao diện tải tạm thời (dạng các khối màu xám mô phỏng layout) để người dùng có cảm giác hệ thống tải nhanh hơn — tăng hiệu năng cảm nhận (Perceived Performance)</v>
       </c>
-      <c r="F18" t="str">
-        <v>Biểu thị sơ đồ cấu trúc xương của nhân vật hoạt hình 3D trong game — đồ họa game 3D</v>
-      </c>
-      <c r="G18" t="str">
-        <v>Đại diện cho chế độ ban đêm (Dark Mode) của ứng dụng di động — chế độ ban đêm</v>
-      </c>
-      <c r="H18" t="str">
-        <v>Đánh dấu các khu vực giao diện đang bị khóa tính năng đối với tài khoản thường — khóa tính năng</v>
-      </c>
       <c r="I18">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="19">
@@ -946,19 +946,19 @@
         <v>Visual Hierarchy và Progressive Disclosure giúp quản lý tải nhận thức. Bằng cách chỉ hiển thị thông tin quan trọng nhất ở cấp độ cao, và cho phép người dùng đi sâu vào chi tiết theo nhu cầu (drill-down), Dashboard sẽ sạch sẽ và hiệu quả hơn.</v>
       </c>
       <c r="E19" t="str">
-        <v>Áp dụng nguyên tắc "progressive disclosure" (tiết lộ thông tin tăng dần): Chỉ hiển thị các chỉ số tổng quan (KPI cards) ở trên cùng; các bảng dữ liệu chi tiết được ẩn trong các tab hoặc cung cấp tính năng drill-down khi bấm vào — tiết lộ thông tin tăng dần</v>
+        <v>Sử dụng 10 tông màu sắc tương phản mạnh khác nhau để tô nền cho từng khối biểu đồ nhằm tạo sự nổi bật tối đa — đa dạng màu sắc gây nhiễu</v>
       </c>
       <c r="F19" t="str">
         <v>Hiển thị tất cả 15 biểu đồ và 5 bảng số liệu chi tiết kích thước bằng nhau trên cùng một màn hình để người dùng có cái nhìn toàn cảnh ngay lập tức — hiển thị đồng bộ bề mặt</v>
       </c>
       <c r="G19" t="str">
-        <v>Sử dụng 10 tông màu sắc tương phản mạnh khác nhau để tô nền cho từng khối biểu đồ nhằm tạo sự nổi bật tối đa — đa dạng màu sắc gây nhiễu</v>
+        <v>Áp dụng nguyên tắc "progressive disclosure" (tiết lộ thông tin tăng dần): Chỉ hiển thị các chỉ số tổng quan (KPI cards) ở trên cùng; các bảng dữ liệu chi tiết được ẩn trong các tab hoặc cung cấp tính năng drill-down khi bấm vào — tiết lộ thông tin tăng dần</v>
       </c>
       <c r="H19" t="str">
         <v>Tự động ẩn toàn bộ các biểu đồ và chỉ hiển thị số liệu dưới dạng file text thô cho nhẹ trang web — tối giản hóa cực đoan</v>
       </c>
       <c r="I19">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -975,19 +975,19 @@
         <v>Mọi tương tác của người dùng cần có phản hồi lập tức để họ biết hệ thống đã ghi nhận hành động. Thiếu phản hồi trong giao dịch tài chính sẽ gây hoang mang, khiến họ bấm nút chuyển tiền nhiều lần gây trùng lặp giao dịch.</v>
       </c>
       <c r="E20" t="str">
-        <v>Hiển thị màn hình trạng thái đang xử lý (Loading screen kèm thông điệp rõ ràng), tiếp theo là màn hình xác nhận kết quả (Thành công/Thất bại có mã giao dịch) kèm âm thanh phản hồi nhẹ và rung phản hồi (haptic) trên điện thoại — phản hồi đa giác quan hệ thống</v>
+        <v>Gửi một email thông báo kết quả sau 24 giờ và yêu cầu người dùng kiểm tra hòm thư rác để nhận thông tin — phản hồi trễ qua email</v>
       </c>
       <c r="F20" t="str">
         <v>Tự động quay về trang chủ ngay lập tức mà không hiển thị thông báo gì, để người dùng tự kiểm tra lại số dư tài khoản xem đã bị trừ tiền chưa — quay về trang chủ âm thầm</v>
       </c>
       <c r="G20" t="str">
+        <v>Hiển thị màn hình trạng thái đang xử lý (Loading screen kèm thông điệp rõ ràng), tiếp theo là màn hình xác nhận kết quả (Thành công/Thất bại có mã giao dịch) kèm âm thanh phản hồi nhẹ và rung phản hồi (haptic) trên điện thoại — phản hồi đa giác quan hệ thống</v>
+      </c>
+      <c r="H20" t="str">
         <v>Hiển thị một popup bắt buộc người dùng phải nhập lại mã OTP một lần nữa để xác nhận họ thực sự muốn chuyển khoản — xác thực lặp thừa</v>
       </c>
-      <c r="H20" t="str">
-        <v>Gửi một email thông báo kết quả sau 24 giờ và yêu cầu người dùng kiểm tra hòm thư rác để nhận thông tin — phản hồi trễ qua email</v>
-      </c>
       <c r="I20">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21">
@@ -1004,19 +1004,19 @@
         <v>Empty States là cơ hội tuyệt vời để tương tác với người dùng. Thay vì dẫn họ vào ngõ cụt (Dead-end), một thiết kế thông minh sẽ khơi gợi nhu cầu và dẫn dắt họ tiếp tục trải nghiệm sản phẩm bằng các nút gợi ý hành động.</v>
       </c>
       <c r="E21" t="str">
+        <v>Để hiển thị bảng danh sách các lập trình viên đã viết ra trang web đó nhằm tăng độ tin cậy thương hiệu — hiển thị danh sách dev</v>
+      </c>
+      <c r="F21" t="str">
         <v>Vì thay vì chỉ hiển thị một trang trắng trơn gây cảm giác cụt luồng, Empty State tốt sẽ giải thích bối cảnh, kết hợp hình ảnh minh họa thân thiện và đưa ra nút CTA hành động tiếp theo (ví dụ: "Mua sắm ngay", "Thử từ khóa khác") — định hướng hành vi tiếp theo</v>
       </c>
-      <c r="F21" t="str">
+      <c r="G21" t="str">
         <v>Để hệ thống tự động tải ngẫu nhiên các sản phẩm giá cao nhất và tự động chèn vào giỏ hàng của khách hàng — tự động chèn đơn hàng</v>
-      </c>
-      <c r="G21" t="str">
-        <v>Để hiển thị bảng danh sách các lập trình viên đã viết ra trang web đó nhằm tăng độ tin cậy thương hiệu — hiển thị danh sách dev</v>
       </c>
       <c r="H21" t="str">
         <v>Để bắt buộc người dùng phải đăng xuất tài khoản và đăng nhập lại bằng một tài khoản khác có nhiều dữ liệu hơn — ép đăng xuất</v>
       </c>
       <c r="I21">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22">
@@ -1033,19 +1033,19 @@
         <v>Accessibility (A11y) là tiêu chuẩn bắt buộc đối với các phần mềm doanh nghiệp hoặc dịch vụ công. BA phải thiết kế các thành phần UI có độ tương phản đạt chuẩn WCAG (thường tối thiểu 4.5:1), hỗ trợ điều hướng hoàn toàn bằng bàn phím (tab index) cho người không dùng được chuột.</v>
       </c>
       <c r="E22" t="str">
+        <v>Để ngăn chặn các cuộc tấn công đánh cắp dữ liệu từ các thiết bị ngoại vi kết nối vào máy chủ — bảo mật thiết bị ngoại vi</v>
+      </c>
+      <c r="F22" t="str">
+        <v>Để phần mềm chạy mượt mà trên các dòng điện thoại di động giá rẻ có cấu hình RAM dưới 1GB — tối ưu hóa phần cứng di động</v>
+      </c>
+      <c r="G22" t="str">
         <v>Để đảm bảo nhân viên bị hạn chế về khả năng (như mù màu, thị lực kém) vẫn có thể vận hành hệ thống thông qua việc tối ưu độ tương phản màu sắc (contrast ratio), hỗ trợ phím tắt và đọc được bằng Screen Reader — hỗ trợ tiếp cận hòa nhập</v>
       </c>
-      <c r="F22" t="str">
+      <c r="H22" t="str">
         <v>Để hệ thống tự động dịch giao diện sang 100 ngôn ngữ khác nhau trên thế giới bằng thuật toán dịch máy Google Translate — dịch thuật giao diện</v>
       </c>
-      <c r="G22" t="str">
-        <v>Để phần mềm chạy mượt mà trên các dòng điện thoại di động giá rẻ có cấu hình RAM dưới 1GB — tối ưu hóa phần cứng di động</v>
-      </c>
-      <c r="H22" t="str">
-        <v>Để ngăn chặn các cuộc tấn công đánh cắp dữ liệu từ các thiết bị ngoại vi kết nối vào máy chủ — bảo mật thiết bị ngoại vi</v>
-      </c>
       <c r="I22">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="23">
@@ -1062,19 +1062,19 @@
         <v>Cognitive Tunneling là hiện tượng tâm lý khi bị stress hoặc quá tập trung, tầm nhìn của con người bị thu hẹp. Nếu thiết kế nút "Hủy đơn" và cảnh báo mất tiền ở góc xa, họ sẽ không thấy. BA phải đưa thông tin quan trọng vào tiêu điểm thị giác trực tiếp (visual anchor).</v>
       </c>
       <c r="E23" t="str">
+        <v>Người dùng liên tục bấm phím F5 để tải lại trang web do tốc độ load quá chậm; BA cần tối ưu hóa các câu lệnh truy vấn SQL ở database — tối ưu hóa cơ sở dữ liệu</v>
+      </c>
+      <c r="F23" t="str">
+        <v>Người dùng từ chối tham gia bài test vì giao diện thiết kế quá xấu và thiếu màu sắc; BA cần thuê designer vẽ lại đồ họa 3D đẹp mắt — thiết kế đồ họa lại</v>
+      </c>
+      <c r="G23" t="str">
         <v>Người dùng quá tập trung vào một khu vực màn hình hoặc một luồng thao tác quen thuộc dẫn đến việc bỏ sót các thông tin cảnh báo quan trọng ở góc khác; BA cần điều chỉnh bằng cách đưa cảnh báo vào giữa tiêu điểm thị giác hoặc dùng popup modal chặn luồng khi có sự cố nghiêm trọng — điều chỉnh tiêu điểm nhận thức</v>
-      </c>
-      <c r="F23" t="str">
-        <v>Người dùng liên tục bấm phím F5 để tải lại trang web do tốc độ load quá chậm; BA cần tối ưu hóa các câu lệnh truy vấn SQL ở database — tối ưu hóa cơ sở dữ liệu</v>
-      </c>
-      <c r="G23" t="str">
-        <v>Người dùng từ chối tham gia bài test vì giao diện thiết kế quá xấu và thiếu màu sắc; BA cần thuê designer vẽ lại đồ họa 3D đẹp mắt — thiết kế đồ họa lại</v>
       </c>
       <c r="H23" t="str">
         <v>Người dùng tự động viết code để vượt qua các bước bảo mật của bản mẫu; BA cần cài đặt thêm phần mềm diệt virus trên máy tính test — diệt virus máy tính</v>
       </c>
       <c r="I23">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24">
@@ -1091,19 +1091,19 @@
         <v>Thumb Zone chỉ ra các vùng trên màn hình di động dễ chạm (Easy), cần với (Stretch) và khó chạm (Ow) khi dùng 1 tay. Thiết kế tốt sẽ đặt các tương tác thường xuyên (như Menu, CTA mua hàng) vào vùng Easy (cạnh dưới màn hình), và các nút nguy hiểm như Xóa tài khoản vào vùng Ow (cạnh trên).</v>
       </c>
       <c r="E24" t="str">
+        <v>Để ngăn chặn người dùng vô tình chạm các ngón tay khác vào màn hình làm loạn cảm ứng — ngăn chạm nhầm</v>
+      </c>
+      <c r="F24" t="str">
+        <v>Vì hệ điều hành iOS và Android bắt buộc tất cả các ứng dụng di động phải đặt nút bấm ở cạnh dưới — quy định hệ điều hành</v>
+      </c>
+      <c r="G24" t="str">
+        <v>Vì ngón tay cái có diện tích tiếp xúc lớn nhất nên cần thiết kế các nút bấm ở cạnh trên màn hình có kích thước nhỏ lại — kích thước nút cạnh trên</v>
+      </c>
+      <c r="H24" t="str">
         <v>Vì ngón tay cái là ngón tay tương tác chủ yếu khi sử dụng điện thoại bằng một tay; các khu vực ở cạnh dưới và giữa màn hình là vùng dễ chạm tới nhất mà không gây mỏi tay — tối ưu hóa vùng chạm một tay</v>
       </c>
-      <c r="F24" t="str">
-        <v>Vì ngón tay cái có diện tích tiếp xúc lớn nhất nên cần thiết kế các nút bấm ở cạnh trên màn hình có kích thước nhỏ lại — kích thước nút cạnh trên</v>
-      </c>
-      <c r="G24" t="str">
-        <v>Để ngăn chặn người dùng vô tình chạm các ngón tay khác vào màn hình làm loạn cảm ứng — ngăn chạm nhầm</v>
-      </c>
-      <c r="H24" t="str">
-        <v>Vì hệ điều hành iOS và Android bắt buộc tất cả các ứng dụng di động phải đặt nút bấm ở cạnh dưới — quy định hệ điều hành</v>
-      </c>
       <c r="I24">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="25">
@@ -1120,19 +1120,19 @@
         <v>Đây là tư duy thiết kế luồng đi linh hoạt (Progressive Profiling). Việc bắt buộc eKYC ngay từ đầu tạo ra rào cản rất lớn (Friction). Trì hoãn việc yêu cầu thông tin nhạy cảm cho đến khi nó thực sự cần thiết (Just-in-time) giúp tăng tỷ lệ chuyển đổi người dùng đăng ký ban đầu.</v>
       </c>
       <c r="E25" t="str">
+        <v>Yêu cầu người dùng phải đến trực tiếp văn phòng chi nhánh để ký giấy tờ trước rồi mới cho phép tải ứng dụng — quy trình thuần truyền thống</v>
+      </c>
+      <c r="F25" t="str">
         <v>Thiết kế luồng eKYC phân cấp: Cho phép người dùng đăng ký tài khoản nhanh bằng số điện thoại để trải nghiệm xem bảng giá trước (MVP); chỉ yêu cầu xác thực eKYC đầy đủ khi họ thực hiện nạp tiền hoặc giao dịch mua bán thực tế — trì hoãn xác thực tăng chuyển đổi</v>
-      </c>
-      <c r="F25" t="str">
-        <v>Bắt buộc người dùng phải hoàn thành toàn bộ 10 bước xác thực bảo mật khắt khe ngay khi vừa mở ứng dụng lần đầu tiên thì mới cho xem thông tin — xác thực khắt khe chặn người dùng</v>
       </c>
       <c r="G25" t="str">
         <v>Loại bỏ hoàn toàn bước chụp ảnh căn cước công dân và ký số để người dùng đăng ký nhanh nhất có thể — vi phạm quy định pháp lý an toàn</v>
       </c>
       <c r="H25" t="str">
-        <v>Yêu cầu người dùng phải đến trực tiếp văn phòng chi nhánh để ký giấy tờ trước rồi mới cho phép tải ứng dụng — quy trình thuần truyền thống</v>
+        <v>Bắt buộc người dùng phải hoàn thành toàn bộ 10 bước xác thực bảo mật khắt khe ngay khi vừa mở ứng dụng lần đầu tiên thì mới cho xem thông tin — xác thực khắt khe chặn người dùng</v>
       </c>
       <c r="I25">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26">
@@ -1155,10 +1155,10 @@
         <v>Người dùng sẽ đưa ra quyết định nhanh hơn nếu hệ thống cung cấp cho họ tối thiểu 50 lựa chọn khác nhau trên cùng một trang — tăng số lượng lựa chọn</v>
       </c>
       <c r="G26" t="str">
+        <v>Quy định rằng menu của website chỉ được phép hiển thị chữ viết chứ không được phép có icon minh họa kèm theo — menu thô</v>
+      </c>
+      <c r="H26" t="str">
         <v>Hệ thống bắt buộc phải tự động chọn ngẫu nhiên một dịch vụ cho khách hàng nếu họ không bấm chọn sau 5 giây — tự động chọn ngẫu nhiên</v>
-      </c>
-      <c r="H26" t="str">
-        <v>Quy định rằng menu của website chỉ được phép hiển thị chữ viết chứ không được phép có icon minh họa kèm theo — menu thô</v>
       </c>
       <c r="I26">
         <v>1</v>
